--- a/resultados_analisisCol/analisis_empresas_20250508.xlsx
+++ b/resultados_analisisCol/analisis_empresas_20250508.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/laura_villalobos-baquero_siemens_com/Documents/Documentos/PythonLinksEmpresas/resultados_analisisCol/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://siemens-my.sharepoint.com/personal/moises_pirela_ext_siemens_com/Documents/CARPETA MOISES/hola/LinksEmpresas/resultados_analisisCol/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="11_434511E79132AE667BB83211595ED87656CD5755" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97E6E18E-D51B-441B-B40B-AC61630F5E22}"/>
